--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Archana\GitHub\Delta1-Automation\KatalonAutomationScripts\DataFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Archana\eclipse-workspace\delta1-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760F90BF-0F21-4DDB-9221-980EE598A22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE411671-167D-43F6-BCE2-A2932605EDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{5F4CC7F0-8BD6-41FD-85C1-DCF17C64A46A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" firstSheet="1" activeTab="3" xr2:uid="{5F4CC7F0-8BD6-41FD-85C1-DCF17C64A46A}"/>
   </bookViews>
   <sheets>
     <sheet name="Holidays" sheetId="13" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="185">
   <si>
     <t>Ticker</t>
   </si>
@@ -458,9 +458,6 @@
   </si>
   <si>
     <t>nov 105</t>
-  </si>
-  <si>
-    <t>Add ticker</t>
   </si>
   <si>
     <t>dec 440</t>
@@ -630,6 +627,9 @@
   </si>
   <si>
     <t>aapl dec 231-mar 280 euroflex jellyroll</t>
+  </si>
+  <si>
+    <t>Run Flag</t>
   </si>
 </sst>
 </file>
@@ -1061,80 +1061,80 @@
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...4050990419</v>
+        <v>#N/A Requesting Data...3430859338</v>
         <stp/>
         <stp>BDP|14014614177385490883</stp>
         <tr r="M11" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3804572932</v>
+        <v>#N/A Requesting Data...3787619886</v>
         <stp/>
         <stp>BDP|17914771070757396967</stp>
         <tr r="M23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4174139679</v>
+        <v>#N/A Requesting Data...4168908045</v>
         <stp/>
         <stp>BDP|12191885856176020024</stp>
         <tr r="M19" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4265444452</v>
+        <v>#N/A Requesting Data...3801937185</v>
         <stp/>
         <stp>BDP|11222918239606141336</stp>
         <tr r="M10" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3670105146</v>
+        <v>#N/A Requesting Data...4140089424</v>
         <stp/>
         <stp>BDP|10651803860804892507</stp>
         <tr r="M20" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3871949820</v>
+        <v>#N/A Requesting Data...3782418861</v>
         <stp/>
         <stp>BDP|11138132499892845425</stp>
         <tr r="B6" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3802653383</v>
+        <v>#N/A Requesting Data...3767758048</v>
         <stp/>
         <stp>BDP|14818210720281309974</stp>
         <tr r="F4" s="4"/>
         <tr r="M24" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3570950592</v>
+        <v>#N/A Requesting Data...3528611091</v>
         <stp/>
         <stp>BDP|17354182839553220513</stp>
         <tr r="M18" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4035949181</v>
+        <v>#N/A Requesting Data...3575389965</v>
         <stp/>
         <stp>BDP|15833637773500916777</stp>
         <tr r="M22" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3738698379</v>
+        <v>#N/A Requesting Data...4057114221</v>
         <stp/>
         <stp>BDP|10553485173797766561</stp>
         <tr r="M17" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4015560628</v>
+        <v>#N/A Requesting Data...3743974885</v>
         <stp/>
         <stp>BDP|10725320790729783234</stp>
         <tr r="M8" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3786430408</v>
+        <v>#N/A Requesting Data...3674646595</v>
         <stp/>
         <stp>BDP|15290075098549931204</stp>
         <tr r="M2" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4075831792</v>
+        <v>#N/A Requesting Data...3783586696</v>
         <stp/>
         <stp>BDP|11090127615376453378</stp>
         <tr r="M13" s="5"/>
@@ -1142,19 +1142,19 @@
     </main>
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...4284588304</v>
+        <v>#N/A Requesting Data...3772909140</v>
         <stp/>
         <stp>BDP|4236539151683226891</stp>
         <tr r="M21" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3675206314</v>
+        <v>#N/A Requesting Data...3973137575</v>
         <stp/>
         <stp>BDP|2613081399981359290</stp>
         <tr r="M12" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4065129490</v>
+        <v>#N/A Requesting Data...4019082344</v>
         <stp/>
         <stp>BDP|2154512199383777756</stp>
         <tr r="M6" s="5"/>
@@ -1172,7 +1172,7 @@
         <tr r="N23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3708480941</v>
+        <v>#N/A Requesting Data...3825298511</v>
         <stp/>
         <stp>BDP|2219595241806083194</stp>
         <tr r="M15" s="5"/>
@@ -1185,37 +1185,37 @@
         <tr r="E16" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4220282427</v>
+        <v>#N/A Requesting Data...3914994541</v>
         <stp/>
         <stp>BDP|7276645360862777315</stp>
         <tr r="M5" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3835661319</v>
+        <v>#N/A Requesting Data...3703920299</v>
         <stp/>
         <stp>BDP|1614643148556376256</stp>
         <tr r="M9" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4125284933</v>
+        <v>#N/A Requesting Data...3932644361</v>
         <stp/>
         <stp>BDP|8389300253224362856</stp>
         <tr r="M4" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4142150298</v>
+        <v>#N/A Requesting Data...4022779209</v>
         <stp/>
         <stp>BDP|1386483162619383929</stp>
         <tr r="M3" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4070706976</v>
+        <v>#N/A Requesting Data...4113389827</v>
         <stp/>
         <stp>BDP|722161999546011081</stp>
         <tr r="M14" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3626690847</v>
+        <v>#N/A Requesting Data...3754933195</v>
         <stp/>
         <stp>BDP|281963796682346956</stp>
         <tr r="M16" s="5"/>
@@ -1822,7 +1822,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -2155,7 +2155,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <f ca="1">R49</f>
@@ -2507,10 +2507,10 @@
         <v>1.583169</v>
       </c>
       <c r="AE16" s="41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF16" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG16" s="43" t="b">
         <f>AF16="Regular Cash"</f>
@@ -2600,10 +2600,10 @@
         <v>1.6383669999999999</v>
       </c>
       <c r="AE17" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF17" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG17" s="43" t="b">
         <f t="shared" ref="AG17:AG80" si="9">AF17="Regular Cash"</f>
@@ -2693,10 +2693,10 @@
         <v>1.5062040000000001</v>
       </c>
       <c r="AE18" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF18" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG18" s="43" t="b">
         <f t="shared" si="9"/>
@@ -2786,10 +2786,10 @@
         <v>1.7814000000000001</v>
       </c>
       <c r="AE19" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF19" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG19" s="43" t="b">
         <f t="shared" si="9"/>
@@ -2879,10 +2879,10 @@
         <v>1.596398</v>
       </c>
       <c r="AE20" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF20" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG20" s="43" t="b">
         <f t="shared" si="9"/>
@@ -2972,10 +2972,10 @@
         <v>1.5768709999999999</v>
       </c>
       <c r="AE21" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF21" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG21" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3068,10 +3068,10 @@
         <v>1.366009</v>
       </c>
       <c r="AE22" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF22" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG22" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3165,10 +3165,10 @@
         <v>1.636431</v>
       </c>
       <c r="AE23" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF23" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG23" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3258,10 +3258,10 @@
         <v>1.4281170000000001</v>
       </c>
       <c r="AE24" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF24" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG24" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3351,10 +3351,10 @@
         <v>1.375875</v>
       </c>
       <c r="AE25" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF25" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG25" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3444,10 +3444,10 @@
         <v>1.2777879999999999</v>
       </c>
       <c r="AE26" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF26" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG26" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3537,10 +3537,10 @@
         <v>1.58</v>
       </c>
       <c r="AE27" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF27" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG27" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3616,10 +3616,10 @@
         <v>1.339224</v>
       </c>
       <c r="AE28" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF28" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG28" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3695,10 +3695,10 @@
         <v>1.366242</v>
       </c>
       <c r="AE29" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF29" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG29" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3774,10 +3774,10 @@
         <v>1.405559</v>
       </c>
       <c r="AE30" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF30" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG30" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3853,10 +3853,10 @@
         <v>1.5699920000000001</v>
       </c>
       <c r="AE31" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF31" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG31" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3893,10 +3893,10 @@
         <v>1.3836189999999999</v>
       </c>
       <c r="AE32" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF32" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG32" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3936,10 +3936,10 @@
         <v>1.43164</v>
       </c>
       <c r="AE33" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF33" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG33" s="43" t="b">
         <f t="shared" si="9"/>
@@ -3976,10 +3976,10 @@
         <v>1.2331190000000001</v>
       </c>
       <c r="AE34" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF34" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG34" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4016,10 +4016,10 @@
         <v>1.4354290000000001</v>
       </c>
       <c r="AE35" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF35" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG35" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4056,10 +4056,10 @@
         <v>1.322611</v>
       </c>
       <c r="AE36" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF36" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG36" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4096,10 +4096,10 @@
         <v>1.245568</v>
       </c>
       <c r="AE37" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF37" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG37" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4141,10 +4141,10 @@
         <v>1.0967750000000001</v>
       </c>
       <c r="AE38" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF38" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG38" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4186,10 +4186,10 @@
         <v>1.3513329999999999</v>
       </c>
       <c r="AE39" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF39" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG39" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4231,10 +4231,10 @@
         <v>1.2345740000000001</v>
       </c>
       <c r="AE40" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF40" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG40" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4276,10 +4276,10 @@
         <v>1.183108</v>
       </c>
       <c r="AE41" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF41" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG41" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4316,10 +4316,10 @@
         <v>1.033118</v>
       </c>
       <c r="AE42" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF42" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG42" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4356,10 +4356,10 @@
         <v>1.3289299999999999</v>
       </c>
       <c r="AE43" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF43" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG43" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4411,10 +4411,10 @@
         <v>1.082068</v>
       </c>
       <c r="AE44" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF44" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG44" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4453,10 +4453,10 @@
         <v>1.0784419999999999</v>
       </c>
       <c r="AE45" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF45" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG45" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4495,10 +4495,10 @@
         <v>1.049604</v>
       </c>
       <c r="AE46" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF46" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG46" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4551,10 +4551,10 @@
         <v>1.2115499999999999</v>
       </c>
       <c r="AE47" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF47" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG47" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4605,10 +4605,10 @@
         <v>1.0334300000000001</v>
       </c>
       <c r="AE48" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF48" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG48" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4659,10 +4659,10 @@
         <v>1.03007</v>
       </c>
       <c r="AE49" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF49" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG49" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4713,10 +4713,10 @@
         <v>0.93081000000000003</v>
       </c>
       <c r="AE50" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF50" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG50" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4767,10 +4767,10 @@
         <v>1.1349199999999999</v>
       </c>
       <c r="AE51" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF51" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG51" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4821,10 +4821,10 @@
         <v>0.93918999999999997</v>
       </c>
       <c r="AE52" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF52" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG52" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4872,10 +4872,10 @@
         <v>0.93669000000000002</v>
       </c>
       <c r="AE53" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF53" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG53" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4923,10 +4923,10 @@
         <v>0.82460999999999995</v>
       </c>
       <c r="AE54" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF54" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG54" s="43" t="b">
         <f t="shared" si="9"/>
@@ -4968,10 +4968,10 @@
         <v>0.98024999999999995</v>
       </c>
       <c r="AE55" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF55" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG55" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5012,10 +5012,10 @@
         <v>0.83794999999999997</v>
       </c>
       <c r="AE56" s="50" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF56" s="50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG56" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5055,10 +5055,10 @@
         <v>0.83911999999999998</v>
       </c>
       <c r="AE57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG57" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5093,10 +5093,10 @@
         <v>0.69372</v>
       </c>
       <c r="AE58" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG58" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5131,10 +5131,10 @@
         <v>1.02183</v>
       </c>
       <c r="AE59" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG59" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5169,10 +5169,10 @@
         <v>0.77944999999999998</v>
       </c>
       <c r="AE60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF60" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG60" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5207,10 +5207,10 @@
         <v>0.68825999999999998</v>
       </c>
       <c r="AE61" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG61" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5242,10 +5242,10 @@
         <v>0.61389000000000005</v>
       </c>
       <c r="AE62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG62" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5277,10 +5277,10 @@
         <v>0.77012999999999998</v>
       </c>
       <c r="AE63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG63" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5315,10 +5315,10 @@
         <v>0.62495000000000001</v>
       </c>
       <c r="AE64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG64" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5360,10 +5360,10 @@
         <v>0.62761999999999996</v>
       </c>
       <c r="AE65" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG65" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5398,10 +5398,10 @@
         <v>0.55332000000000003</v>
       </c>
       <c r="AE66" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG66" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5433,10 +5433,10 @@
         <v>0.65276000000000001</v>
       </c>
       <c r="AE67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG67" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5471,10 +5471,10 @@
         <v>0.60213000000000005</v>
       </c>
       <c r="AE68" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG68" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5516,10 +5516,10 @@
         <v>0.53127999999999997</v>
       </c>
       <c r="AE69" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF69" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG69" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5554,10 +5554,10 @@
         <v>0.48037999999999997</v>
       </c>
       <c r="AE70" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF70" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG70" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5592,10 +5592,10 @@
         <v>0.59018999999999999</v>
       </c>
       <c r="AE71" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF71" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG71" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5627,10 +5627,10 @@
         <v>0.50832999999999995</v>
       </c>
       <c r="AE72" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG72" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5662,10 +5662,10 @@
         <v>0.51819000000000004</v>
       </c>
       <c r="AE73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG73" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5700,10 +5700,10 @@
         <v>0.56142999999999998</v>
       </c>
       <c r="AE74" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF74" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG74" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5736,10 +5736,10 @@
         <v>0.71933999999999998</v>
       </c>
       <c r="AE75" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF75" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG75" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5774,10 +5774,10 @@
         <v>0.69091999999999998</v>
       </c>
       <c r="AE76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF76" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG76" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5809,10 +5809,10 @@
         <v>0.66922000000000004</v>
       </c>
       <c r="AE77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG77" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5847,10 +5847,10 @@
         <v>0.64195000000000002</v>
       </c>
       <c r="AE78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG78" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5885,10 +5885,10 @@
         <v>0.77541000000000004</v>
       </c>
       <c r="AE79" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF79" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG79" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5923,10 +5923,10 @@
         <v>0.71872000000000003</v>
       </c>
       <c r="AE80" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF80" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG80" s="43" t="b">
         <f t="shared" si="9"/>
@@ -5958,10 +5958,10 @@
         <v>0.65559999999999996</v>
       </c>
       <c r="AE81" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF81" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG81" s="43" t="b">
         <f t="shared" ref="AG81:AG95" si="13">AF81="Regular Cash"</f>
@@ -5993,10 +5993,10 @@
         <v>0.55127000000000004</v>
       </c>
       <c r="AE82" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF82" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG82" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6028,10 +6028,10 @@
         <v>0.79264999999999997</v>
       </c>
       <c r="AE83" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF83" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG83" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6063,10 +6063,10 @@
         <v>0.57933999999999997</v>
       </c>
       <c r="AE84" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF84" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG84" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6098,10 +6098,10 @@
         <v>0.55547000000000002</v>
       </c>
       <c r="AE85" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF85" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG85" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6133,10 +6133,10 @@
         <v>0.51946999999999999</v>
       </c>
       <c r="AE86" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF86" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG86" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6168,10 +6168,10 @@
         <v>0.67166999999999999</v>
       </c>
       <c r="AE87" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF87" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG87" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6203,10 +6203,10 @@
         <v>0.52168999999999999</v>
       </c>
       <c r="AE88" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF88" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG88" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6238,10 +6238,10 @@
         <v>0.48762</v>
       </c>
       <c r="AE89" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF89" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG89" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6273,10 +6273,10 @@
         <v>0.46709000000000001</v>
       </c>
       <c r="AE90" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF90" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG90" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6308,10 +6308,10 @@
         <v>0.56789000000000001</v>
       </c>
       <c r="AE91" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF91" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG91" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6343,10 +6343,10 @@
         <v>0.35102</v>
       </c>
       <c r="AE92" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF92" t="s">
         <v>139</v>
-      </c>
-      <c r="AF92" t="s">
-        <v>140</v>
       </c>
       <c r="AG92" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6378,10 +6378,10 @@
         <v>0.46877999999999997</v>
       </c>
       <c r="AE93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG93" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6413,10 +6413,10 @@
         <v>0.41376000000000002</v>
       </c>
       <c r="AE94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF94" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG94" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6448,10 +6448,10 @@
         <v>0.39476</v>
       </c>
       <c r="AE95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG95" s="43" t="b">
         <f t="shared" si="13"/>
@@ -6483,10 +6483,10 @@
         <v>0.51558999999999999</v>
       </c>
       <c r="AE96" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI96" s="20"/>
     </row>
@@ -6507,10 +6507,10 @@
         <v>0.40006000000000003</v>
       </c>
       <c r="AE97" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF97" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI97" s="20"/>
     </row>
@@ -6531,10 +6531,10 @@
         <v>0.36025000000000001</v>
       </c>
       <c r="AE98" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF98" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI98" s="20"/>
     </row>
@@ -6555,10 +6555,10 @@
         <v>0.35437999999999997</v>
       </c>
       <c r="AE99" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF99" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI99" s="20"/>
     </row>
@@ -6579,10 +6579,10 @@
         <v>0.43584000000000001</v>
       </c>
       <c r="AE100" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF100" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI100" s="20"/>
     </row>
@@ -6603,10 +6603,10 @@
         <v>0.37809999999999999</v>
       </c>
       <c r="AE101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF101" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI101" s="20"/>
     </row>
@@ -6627,10 +6627,10 @@
         <v>0.35337000000000002</v>
       </c>
       <c r="AE102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI102" s="20"/>
     </row>
@@ -6651,10 +6651,10 @@
         <v>0.33098</v>
       </c>
       <c r="AE103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI103" s="20"/>
     </row>
@@ -6675,10 +6675,10 @@
         <v>0.39277000000000001</v>
       </c>
       <c r="AE104" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF104" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI104" s="20"/>
     </row>
@@ -6699,10 +6699,10 @@
         <v>0.36899999999999999</v>
       </c>
       <c r="AE105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI105" s="20"/>
     </row>
@@ -6723,10 +6723,10 @@
         <v>0.34644000000000003</v>
       </c>
       <c r="AE106" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF106" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI106" s="20"/>
     </row>
@@ -6747,10 +6747,10 @@
         <v>0.31551000000000001</v>
       </c>
       <c r="AE107" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF107" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI107" s="20"/>
     </row>
@@ -6771,10 +6771,10 @@
         <v>0.41132999999999997</v>
       </c>
       <c r="AE108" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF108" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI108" s="20"/>
     </row>
@@ -6795,10 +6795,10 @@
         <v>0.37531900000000001</v>
       </c>
       <c r="AE109" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF109" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI109" s="20"/>
     </row>
@@ -6819,10 +6819,10 @@
         <v>0.348408</v>
       </c>
       <c r="AE110" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI110" s="20"/>
     </row>
@@ -6843,10 +6843,10 @@
         <v>0.37082300000000001</v>
       </c>
       <c r="AE111" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF111" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI111" s="20"/>
     </row>
@@ -6867,10 +6867,10 @@
         <v>0.34755200000000003</v>
       </c>
       <c r="AE112" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF112" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI112" s="20"/>
     </row>
@@ -6891,10 +6891,10 @@
         <v>0.37221799999999999</v>
       </c>
       <c r="AE113" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI113" s="20"/>
     </row>
@@ -6915,10 +6915,10 @@
         <v>0.40497</v>
       </c>
       <c r="AE114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF114" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI114" s="20"/>
     </row>
@@ -6939,10 +6939,10 @@
         <v>0.319853</v>
       </c>
       <c r="AE115" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI115" s="20"/>
     </row>
@@ -6963,10 +6963,10 @@
         <v>0.39182299999999998</v>
       </c>
       <c r="AE116" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF116" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI116" s="20"/>
     </row>
@@ -6987,10 +6987,10 @@
         <v>0.35853000000000002</v>
       </c>
       <c r="AE117" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF117" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI117" s="20"/>
     </row>
@@ -7011,10 +7011,10 @@
         <v>0.35200999999999999</v>
       </c>
       <c r="AE118" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF118" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI118" s="20"/>
     </row>
@@ -7038,10 +7038,10 @@
         <v>0.31342100000000001</v>
       </c>
       <c r="AE119" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF119" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI119" s="20"/>
     </row>
@@ -7062,10 +7062,10 @@
         <v>0.37950400000000001</v>
       </c>
       <c r="AE120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF120" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI120" s="20"/>
     </row>
@@ -7086,10 +7086,10 @@
         <v>0.34835500000000003</v>
       </c>
       <c r="AE121" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF121" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI121" s="20"/>
     </row>
@@ -7110,10 +7110,10 @@
         <v>0.34995300000000001</v>
       </c>
       <c r="AE122" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF122" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI122" s="20"/>
     </row>
@@ -7134,10 +7134,10 @@
         <v>0.29925800000000002</v>
       </c>
       <c r="AE123" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF123" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI123" s="20"/>
     </row>
@@ -7158,10 +7158,10 @@
         <v>0.04</v>
       </c>
       <c r="AE124" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AF124" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AI124" s="20"/>
     </row>
@@ -7182,10 +7182,10 @@
         <v>0.28681000000000001</v>
       </c>
       <c r="AE125" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF125" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI125" s="20"/>
     </row>
@@ -7206,10 +7206,10 @@
         <v>0.08</v>
       </c>
       <c r="AE126" t="s">
+        <v>141</v>
+      </c>
+      <c r="AF126" t="s">
         <v>142</v>
-      </c>
-      <c r="AF126" t="s">
-        <v>143</v>
       </c>
       <c r="AI126" s="20"/>
     </row>
@@ -7230,10 +7230,10 @@
         <v>0.35193999999999998</v>
       </c>
       <c r="AE127" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF127" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI127" s="20"/>
     </row>
@@ -7254,10 +7254,10 @@
         <v>0.35093999999999997</v>
       </c>
       <c r="AE128" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF128" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI128" s="20"/>
     </row>
@@ -7278,10 +7278,10 @@
         <v>0.28544999999999998</v>
       </c>
       <c r="AE129" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF129" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI129" s="20"/>
     </row>
@@ -7302,10 +7302,10 @@
         <v>0.372</v>
       </c>
       <c r="AE130" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF130" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI130" s="20"/>
     </row>
@@ -7326,10 +7326,10 @@
         <v>0.31225999999999998</v>
       </c>
       <c r="AE131" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF131" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI131" s="20"/>
     </row>
@@ -7350,10 +7350,10 @@
         <v>0.31620999999999999</v>
       </c>
       <c r="AE132" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF132" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI132" s="20"/>
     </row>
@@ -7374,10 +7374,10 @@
         <v>0.26822000000000001</v>
       </c>
       <c r="AE133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF133" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI133" s="20"/>
     </row>
@@ -7398,10 +7398,10 @@
         <v>0.36273</v>
       </c>
       <c r="AE134" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI134" s="20"/>
     </row>
@@ -7422,10 +7422,10 @@
         <v>0.28817999999999999</v>
       </c>
       <c r="AE135" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF135" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI135" s="20"/>
     </row>
@@ -7446,10 +7446,10 @@
         <v>0.30497600000000002</v>
       </c>
       <c r="AE136" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF136" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI136" s="20"/>
     </row>
@@ -7470,10 +7470,10 @@
         <v>0.27117000000000002</v>
       </c>
       <c r="AE137" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF137" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI137" s="20"/>
     </row>
@@ -7494,10 +7494,10 @@
         <v>0.28723900000000002</v>
       </c>
       <c r="AE138" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF138" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI138" s="20"/>
     </row>
@@ -7518,10 +7518,10 @@
         <v>0.28618700000000002</v>
       </c>
       <c r="AE139" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF139" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI139" s="20"/>
     </row>
@@ -7542,10 +7542,10 @@
         <v>0.31802000000000002</v>
       </c>
       <c r="AE140" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI140" s="20"/>
     </row>
@@ -7566,10 +7566,10 @@
         <v>0.2132</v>
       </c>
       <c r="AE141" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AF141" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AI141" s="20"/>
     </row>
@@ -7998,7 +7998,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -8008,57 +8008,66 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1B2C69D-3C24-4835-AFB2-F52E95197AE9}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
       <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>1500</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>114</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>-1.234</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>2500</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>2.0049999999999999</v>
       </c>
     </row>
@@ -8078,76 +8087,115 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0A11DE-B42B-4BB8-A3A8-319DBEBCBB54}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="6.1796875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="32.90625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="6.1796875" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -8157,43 +8205,61 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3366916-357D-497F-A92B-E1F6043DE334}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="6" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -8214,7 +8280,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -8231,7 +8297,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -8267,7 +8333,7 @@
     </row>
     <row r="4" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
@@ -8285,10 +8351,10 @@
     </row>
     <row r="5" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C5" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8313,7 +8379,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -8333,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C2" t="str">
         <f>SUBSTITUTE(B2, CHAR(10), "|")</f>
@@ -8351,7 +8417,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C3" t="str">
         <f>SUBSTITUTE(B3, CHAR(10), "|")</f>
@@ -8385,8 +8451,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="77" t="s">
-        <v>18</v>
+      <c r="A1" t="s">
+        <v>184</v>
       </c>
       <c r="B1" s="77" t="s">
         <v>2</v>
@@ -8407,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="H1" s="77" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -8415,7 +8481,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="76" t="str">
         <f t="shared" ref="C2:C8" si="0">SUBSTITUTE(B2, CHAR(10), "|")</f>
@@ -8436,7 +8502,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="76" t="str">
         <f t="shared" si="0"/>
@@ -8452,10 +8518,10 @@
         <v>-0.44</v>
       </c>
       <c r="G3" s="76" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H3" s="76" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -8463,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="76" t="str">
         <f t="shared" si="0"/>
@@ -8479,10 +8545,10 @@
         <v>-0.44</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H4" s="76" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -8490,7 +8556,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C5" s="76" t="str">
         <f t="shared" si="0"/>
@@ -8506,10 +8572,10 @@
         <v>0.46</v>
       </c>
       <c r="G5" s="76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H5" s="76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
@@ -8517,7 +8583,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="76" t="str">
         <f t="shared" si="0"/>
@@ -8533,10 +8599,10 @@
         <v>-1.36</v>
       </c>
       <c r="G6" s="76" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="76" t="s">
         <v>155</v>
-      </c>
-      <c r="H6" s="76" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -8544,7 +8610,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C7" s="76" t="str">
         <f t="shared" si="0"/>
@@ -8560,7 +8626,7 @@
         <v>-0.15</v>
       </c>
       <c r="G7" s="76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H7" s="78">
         <v>12663</v>
@@ -8571,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C8" s="76" t="str">
         <f t="shared" si="0"/>
@@ -8587,7 +8653,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="G8" s="76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H8" s="78">
         <v>23986</v>
@@ -8600,138 +8666,159 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E85F479-FA2C-489D-859F-F77089D48D16}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" s="1" t="str">
-        <f t="shared" ref="B2:B6" si="0">SUBSTITUTE(A2, CHAR(10), "|")</f>
+    <row r="2" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f t="shared" ref="C2:C6" si="0">SUBSTITUTE(B2, CHAR(10), "|")</f>
         <v>/add  BRK/B Nov 121.5 euroflex</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="1" t="str">
         <f t="shared" si="0"/>
         <v>/add  IBM Nov 121.5 euroflex</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>/add  IBM Nov 121.5 euro</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>/add  IBM Nov - Dec 121.5 jr euro</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="145" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>/add NVDA Nov 140 Euroflex RevCon 9000x traded 0.545 paid to reverse</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="1" t="str">
-        <f>SUBSTITUTE(A7, CHAR(10), "|")</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>SUBSTITUTE(B7, CHAR(10), "|")</f>
         <v>/add JNJ today 165 ef strike 0.5b - looking to reverse 168x</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
     </row>
@@ -8772,7 +8859,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -9588,7 +9675,7 @@
       </c>
       <c r="N23">
         <f>IF(M23="USD",1,_xll.BDP(M23&amp;" Curncy", "PX_LAST"))</f>
-        <v>1.3855999999999999</v>
+        <v>1.357</v>
       </c>
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>
@@ -9602,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C24" s="24">
         <v>45275</v>
@@ -9611,7 +9698,7 @@
         <v>440</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H24">
         <v>1.8633</v>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Archana\eclipse-workspace\delta1-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE411671-167D-43F6-BCE2-A2932605EDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E0A6EF-6ECA-4203-B58B-04EC01C07160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" firstSheet="1" activeTab="3" xr2:uid="{5F4CC7F0-8BD6-41FD-85C1-DCF17C64A46A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" firstSheet="1" activeTab="1" xr2:uid="{5F4CC7F0-8BD6-41FD-85C1-DCF17C64A46A}"/>
   </bookViews>
   <sheets>
     <sheet name="Holidays" sheetId="13" r:id="rId1"/>
-    <sheet name="Add tickers to portfolio" sheetId="1" r:id="rId2"/>
+    <sheet name="AddTickers" sheetId="1" r:id="rId2"/>
     <sheet name="Blotter Validations" sheetId="14" r:id="rId3"/>
     <sheet name="BotCommands" sheetId="2" r:id="rId4"/>
     <sheet name="TC014_DP-2260" sheetId="10" r:id="rId5"/>
@@ -1061,80 +1061,80 @@
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...3430859338</v>
+        <v>#N/A Requesting Data...3689127776</v>
         <stp/>
         <stp>BDP|14014614177385490883</stp>
         <tr r="M11" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3787619886</v>
+        <v>#N/A Requesting Data...3627122317</v>
         <stp/>
         <stp>BDP|17914771070757396967</stp>
         <tr r="M23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4168908045</v>
+        <v>#N/A Requesting Data...4116552338</v>
         <stp/>
         <stp>BDP|12191885856176020024</stp>
         <tr r="M19" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3801937185</v>
+        <v>#N/A Requesting Data...3756918296</v>
         <stp/>
         <stp>BDP|11222918239606141336</stp>
         <tr r="M10" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4140089424</v>
+        <v>#N/A Requesting Data...4015068224</v>
         <stp/>
         <stp>BDP|10651803860804892507</stp>
         <tr r="M20" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3782418861</v>
+        <v>#N/A Requesting Data...3855679841</v>
         <stp/>
         <stp>BDP|11138132499892845425</stp>
         <tr r="B6" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3767758048</v>
+        <v>#N/A Requesting Data...3336474272</v>
         <stp/>
         <stp>BDP|14818210720281309974</stp>
         <tr r="F4" s="4"/>
         <tr r="M24" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3528611091</v>
+        <v>#N/A Requesting Data...3772893482</v>
         <stp/>
         <stp>BDP|17354182839553220513</stp>
         <tr r="M18" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3575389965</v>
+        <v>#N/A Requesting Data...3528778928</v>
         <stp/>
         <stp>BDP|15833637773500916777</stp>
         <tr r="M22" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4057114221</v>
+        <v>#N/A Requesting Data...4150091446</v>
         <stp/>
         <stp>BDP|10553485173797766561</stp>
         <tr r="M17" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3743974885</v>
+        <v>#N/A Requesting Data...3213968450</v>
         <stp/>
         <stp>BDP|10725320790729783234</stp>
         <tr r="M8" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3674646595</v>
+        <v>#N/A Requesting Data...4151063015</v>
         <stp/>
         <stp>BDP|15290075098549931204</stp>
         <tr r="M2" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3783586696</v>
+        <v>#N/A Requesting Data...4283927025</v>
         <stp/>
         <stp>BDP|11090127615376453378</stp>
         <tr r="M13" s="5"/>
@@ -1142,19 +1142,19 @@
     </main>
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...3772909140</v>
+        <v>#N/A Requesting Data...3405367639</v>
         <stp/>
         <stp>BDP|4236539151683226891</stp>
         <tr r="M21" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3973137575</v>
+        <v>#N/A Requesting Data...3322533595</v>
         <stp/>
         <stp>BDP|2613081399981359290</stp>
         <tr r="M12" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4019082344</v>
+        <v>#N/A Requesting Data...3382180936</v>
         <stp/>
         <stp>BDP|2154512199383777756</stp>
         <tr r="M6" s="5"/>
@@ -1172,7 +1172,7 @@
         <tr r="N23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3825298511</v>
+        <v>#N/A Requesting Data...3464180546</v>
         <stp/>
         <stp>BDP|2219595241806083194</stp>
         <tr r="M15" s="5"/>
@@ -1185,37 +1185,37 @@
         <tr r="E16" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3914994541</v>
+        <v>#N/A Requesting Data...3490270653</v>
         <stp/>
         <stp>BDP|7276645360862777315</stp>
         <tr r="M5" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3703920299</v>
+        <v>#N/A Requesting Data...4026368147</v>
         <stp/>
         <stp>BDP|1614643148556376256</stp>
         <tr r="M9" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3932644361</v>
+        <v>#N/A Requesting Data...3471357210</v>
         <stp/>
         <stp>BDP|8389300253224362856</stp>
         <tr r="M4" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4022779209</v>
+        <v>#N/A Requesting Data...3739426020</v>
         <stp/>
         <stp>BDP|1386483162619383929</stp>
         <tr r="M3" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4113389827</v>
+        <v>#N/A Requesting Data...4184503431</v>
         <stp/>
         <stp>BDP|722161999546011081</stp>
         <tr r="M14" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3754933195</v>
+        <v>#N/A Requesting Data...3861328267</v>
         <stp/>
         <stp>BDP|281963796682346956</stp>
         <tr r="M16" s="5"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="N23">
         <f>IF(M23="USD",1,_xll.BDP(M23&amp;" Curncy", "PX_LAST"))</f>
-        <v>1.357</v>
+        <v>1.3586</v>
       </c>
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Archana\eclipse-workspace\delta1-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E0A6EF-6ECA-4203-B58B-04EC01C07160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D74CDE-0F31-433C-B311-D89CF5B1FF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" firstSheet="1" activeTab="1" xr2:uid="{5F4CC7F0-8BD6-41FD-85C1-DCF17C64A46A}"/>
   </bookViews>
@@ -1061,80 +1061,80 @@
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...3689127776</v>
+        <v>#N/A Requesting Data...3116730286</v>
         <stp/>
         <stp>BDP|14014614177385490883</stp>
         <tr r="M11" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3627122317</v>
+        <v>#N/A Requesting Data...3323881689</v>
         <stp/>
         <stp>BDP|17914771070757396967</stp>
         <tr r="M23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4116552338</v>
+        <v>#N/A Requesting Data...1831997750</v>
         <stp/>
         <stp>BDP|12191885856176020024</stp>
         <tr r="M19" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3756918296</v>
+        <v>#N/A Requesting Data...3539005372</v>
         <stp/>
         <stp>BDP|11222918239606141336</stp>
         <tr r="M10" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4015068224</v>
+        <v>#N/A Requesting Data...1921182470</v>
         <stp/>
         <stp>BDP|10651803860804892507</stp>
         <tr r="M20" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3855679841</v>
+        <v>#N/A Requesting Data...2863434980</v>
         <stp/>
         <stp>BDP|11138132499892845425</stp>
         <tr r="B6" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3336474272</v>
+        <v>#N/A Requesting Data...2809252556</v>
         <stp/>
         <stp>BDP|14818210720281309974</stp>
         <tr r="F4" s="4"/>
         <tr r="M24" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3772893482</v>
+        <v>#N/A Requesting Data...3915597306</v>
         <stp/>
         <stp>BDP|17354182839553220513</stp>
         <tr r="M18" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3528778928</v>
+        <v>#N/A Requesting Data...2702786370</v>
         <stp/>
         <stp>BDP|15833637773500916777</stp>
         <tr r="M22" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4150091446</v>
+        <v>#N/A Requesting Data...3858587456</v>
         <stp/>
         <stp>BDP|10553485173797766561</stp>
         <tr r="M17" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3213968450</v>
+        <v>#N/A Requesting Data...2028483817</v>
         <stp/>
         <stp>BDP|10725320790729783234</stp>
         <tr r="M8" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4151063015</v>
+        <v>#N/A Requesting Data...2905634664</v>
         <stp/>
         <stp>BDP|15290075098549931204</stp>
         <tr r="M2" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4283927025</v>
+        <v>#N/A Requesting Data...1818396705</v>
         <stp/>
         <stp>BDP|11090127615376453378</stp>
         <tr r="M13" s="5"/>
@@ -1142,19 +1142,19 @@
     </main>
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...3405367639</v>
+        <v>#N/A Requesting Data...2463032671</v>
         <stp/>
         <stp>BDP|4236539151683226891</stp>
         <tr r="M21" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3322533595</v>
+        <v>#N/A Requesting Data...3415227157</v>
         <stp/>
         <stp>BDP|2613081399981359290</stp>
         <tr r="M12" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3382180936</v>
+        <v>#N/A Requesting Data...2945205562</v>
         <stp/>
         <stp>BDP|2154512199383777756</stp>
         <tr r="M6" s="5"/>
@@ -1172,7 +1172,7 @@
         <tr r="N23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3464180546</v>
+        <v>#N/A Requesting Data...4254932893</v>
         <stp/>
         <stp>BDP|2219595241806083194</stp>
         <tr r="M15" s="5"/>
@@ -1185,37 +1185,37 @@
         <tr r="E16" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3490270653</v>
+        <v>#N/A Requesting Data...3813285549</v>
         <stp/>
         <stp>BDP|7276645360862777315</stp>
         <tr r="M5" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4026368147</v>
+        <v>#N/A Requesting Data...3271659411</v>
         <stp/>
         <stp>BDP|1614643148556376256</stp>
         <tr r="M9" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3471357210</v>
+        <v>#N/A Requesting Data...3800748930</v>
         <stp/>
         <stp>BDP|8389300253224362856</stp>
         <tr r="M4" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3739426020</v>
+        <v>#N/A Requesting Data...3710702205</v>
         <stp/>
         <stp>BDP|1386483162619383929</stp>
         <tr r="M3" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4184503431</v>
+        <v>#N/A Requesting Data...2644152884</v>
         <stp/>
         <stp>BDP|722161999546011081</stp>
         <tr r="M14" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3861328267</v>
+        <v>#N/A Requesting Data...2559657153</v>
         <stp/>
         <stp>BDP|281963796682346956</stp>
         <tr r="M16" s="5"/>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Archana\eclipse-workspace\delta1-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D74CDE-0F31-433C-B311-D89CF5B1FF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD8014B-F10A-4EA3-B968-9500E9408777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" firstSheet="1" activeTab="1" xr2:uid="{5F4CC7F0-8BD6-41FD-85C1-DCF17C64A46A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="2" xr2:uid="{5F4CC7F0-8BD6-41FD-85C1-DCF17C64A46A}"/>
   </bookViews>
   <sheets>
     <sheet name="Holidays" sheetId="13" r:id="rId1"/>
     <sheet name="AddTickers" sheetId="1" r:id="rId2"/>
-    <sheet name="Blotter Validations" sheetId="14" r:id="rId3"/>
+    <sheet name="BlotterValidations" sheetId="14" r:id="rId3"/>
     <sheet name="BotCommands" sheetId="2" r:id="rId4"/>
     <sheet name="TC014_DP-2260" sheetId="10" r:id="rId5"/>
     <sheet name="Import Intraday trades" sheetId="9" r:id="rId6"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="190">
   <si>
     <t>Ticker</t>
   </si>
@@ -587,9 +587,6 @@
     <t>Date</t>
   </si>
   <si>
-    <t>Expiration</t>
-  </si>
-  <si>
     <t>MSFT,INTC</t>
   </si>
   <si>
@@ -630,6 +627,26 @@
   </si>
   <si>
     <t>Run Flag</t>
+  </si>
+  <si>
+    <t>Tickers</t>
+  </si>
+  <si>
+    <t>Expirations</t>
+  </si>
+  <si>
+    <t>Mar6/Mar20</t>
+  </si>
+  <si>
+    <t>APR
+Mar/May</t>
+  </si>
+  <si>
+    <t>Apr
+Mar</t>
+  </si>
+  <si>
+    <t>Mar'25</t>
   </si>
 </sst>
 </file>
@@ -1061,80 +1078,80 @@
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...3116730286</v>
+        <v>#N/A Requesting Data...4102721116</v>
         <stp/>
         <stp>BDP|14014614177385490883</stp>
         <tr r="M11" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3323881689</v>
+        <v>#N/A Requesting Data...4200943786</v>
         <stp/>
         <stp>BDP|17914771070757396967</stp>
         <tr r="M23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1831997750</v>
+        <v>#N/A Requesting Data...2523175019</v>
         <stp/>
         <stp>BDP|12191885856176020024</stp>
         <tr r="M19" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3539005372</v>
+        <v>#N/A Requesting Data...4026482984</v>
         <stp/>
         <stp>BDP|11222918239606141336</stp>
         <tr r="M10" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1921182470</v>
+        <v>#N/A Requesting Data...3334715772</v>
         <stp/>
         <stp>BDP|10651803860804892507</stp>
         <tr r="M20" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2863434980</v>
+        <v>#N/A Requesting Data...4247554339</v>
         <stp/>
         <stp>BDP|11138132499892845425</stp>
         <tr r="B6" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2809252556</v>
+        <v>#N/A Requesting Data...3479047769</v>
         <stp/>
         <stp>BDP|14818210720281309974</stp>
         <tr r="F4" s="4"/>
         <tr r="M24" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3915597306</v>
+        <v>#N/A Requesting Data...3481003590</v>
         <stp/>
         <stp>BDP|17354182839553220513</stp>
         <tr r="M18" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2702786370</v>
+        <v>#N/A Requesting Data...2961707860</v>
         <stp/>
         <stp>BDP|15833637773500916777</stp>
         <tr r="M22" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3858587456</v>
+        <v>#N/A Requesting Data...3116270412</v>
         <stp/>
         <stp>BDP|10553485173797766561</stp>
         <tr r="M17" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2028483817</v>
+        <v>#N/A Requesting Data...3772991957</v>
         <stp/>
         <stp>BDP|10725320790729783234</stp>
         <tr r="M8" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2905634664</v>
+        <v>#N/A Requesting Data...3498445539</v>
         <stp/>
         <stp>BDP|15290075098549931204</stp>
         <tr r="M2" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...1818396705</v>
+        <v>#N/A Requesting Data...3630203178</v>
         <stp/>
         <stp>BDP|11090127615376453378</stp>
         <tr r="M13" s="5"/>
@@ -1142,19 +1159,19 @@
     </main>
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...2463032671</v>
+        <v>#N/A Requesting Data...3760933913</v>
         <stp/>
         <stp>BDP|4236539151683226891</stp>
         <tr r="M21" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3415227157</v>
+        <v>#N/A Requesting Data...4277886170</v>
         <stp/>
         <stp>BDP|2613081399981359290</stp>
         <tr r="M12" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2945205562</v>
+        <v>#N/A Requesting Data...2989371238</v>
         <stp/>
         <stp>BDP|2154512199383777756</stp>
         <tr r="M6" s="5"/>
@@ -1172,7 +1189,7 @@
         <tr r="N23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4254932893</v>
+        <v>#N/A Requesting Data...4075602171</v>
         <stp/>
         <stp>BDP|2219595241806083194</stp>
         <tr r="M15" s="5"/>
@@ -1185,37 +1202,37 @@
         <tr r="E16" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3813285549</v>
+        <v>#N/A Requesting Data...3421479459</v>
         <stp/>
         <stp>BDP|7276645360862777315</stp>
         <tr r="M5" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3271659411</v>
+        <v>#N/A Requesting Data...2591271917</v>
         <stp/>
         <stp>BDP|1614643148556376256</stp>
         <tr r="M9" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3800748930</v>
+        <v>#N/A Requesting Data...4290396496</v>
         <stp/>
         <stp>BDP|8389300253224362856</stp>
         <tr r="M4" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3710702205</v>
+        <v>#N/A Requesting Data...3604426337</v>
         <stp/>
         <stp>BDP|1386483162619383929</stp>
         <tr r="M3" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2644152884</v>
+        <v>#N/A Requesting Data...3084482444</v>
         <stp/>
         <stp>BDP|722161999546011081</stp>
         <tr r="M14" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2559657153</v>
+        <v>#N/A Requesting Data...3281902747</v>
         <stp/>
         <stp>BDP|281963796682346956</stp>
         <tr r="M16" s="5"/>
@@ -8013,7 +8030,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
@@ -8096,7 +8113,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -8139,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -8147,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -8155,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -8163,7 +8180,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -8171,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -8179,7 +8196,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -8187,7 +8204,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -8195,7 +8212,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -8205,21 +8222,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3366916-357D-497F-A92B-E1F6043DE334}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" t="s">
         <v>184</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -8235,7 +8253,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
@@ -8243,7 +8261,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -8251,7 +8269,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
@@ -8259,7 +8277,42 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -8280,7 +8333,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -8379,7 +8432,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -8452,7 +8505,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" s="77" t="s">
         <v>2</v>
@@ -8678,7 +8731,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -8859,7 +8912,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -9675,7 +9728,7 @@
       </c>
       <c r="N23">
         <f>IF(M23="USD",1,_xll.BDP(M23&amp;" Curncy", "PX_LAST"))</f>
-        <v>1.3586</v>
+        <v>1.3717999999999999</v>
       </c>
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Archana\eclipse-workspace\delta1-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD8014B-F10A-4EA3-B968-9500E9408777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDB2052-953C-4021-B9D7-6BF868B13190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="2" xr2:uid="{5F4CC7F0-8BD6-41FD-85C1-DCF17C64A46A}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="198">
   <si>
     <t>Ticker</t>
   </si>
@@ -647,6 +647,32 @@
   </si>
   <si>
     <t>Mar'25</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Apr/Jun</t>
+  </si>
+  <si>
+    <t>FOUR</t>
+  </si>
+  <si>
+    <t>Mar'27/Apr</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Apr
+Mar'27/Apr</t>
+  </si>
+  <si>
+    <t>May8/Jan4
+Apr24</t>
   </si>
 </sst>
 </file>
@@ -923,7 +949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1056,6 +1082,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1078,80 +1107,80 @@
   <volType type="realTimeData">
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...4102721116</v>
+        <v>#N/A Requesting Data...1046207528</v>
         <stp/>
         <stp>BDP|14014614177385490883</stp>
         <tr r="M11" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4200943786</v>
+        <v>#N/A Requesting Data...1962430679</v>
         <stp/>
         <stp>BDP|17914771070757396967</stp>
         <tr r="M23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2523175019</v>
+        <v>#N/A Requesting Data...730921660</v>
         <stp/>
         <stp>BDP|12191885856176020024</stp>
         <tr r="M19" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4026482984</v>
+        <v>#N/A Requesting Data...4199425686</v>
         <stp/>
         <stp>BDP|11222918239606141336</stp>
         <tr r="M10" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3334715772</v>
+        <v>#N/A Requesting Data...1723627710</v>
         <stp/>
         <stp>BDP|10651803860804892507</stp>
         <tr r="M20" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4247554339</v>
+        <v>#N/A Requesting Data...1460464719</v>
         <stp/>
         <stp>BDP|11138132499892845425</stp>
         <tr r="B6" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3479047769</v>
+        <v>#N/A Requesting Data...1006319567</v>
         <stp/>
         <stp>BDP|14818210720281309974</stp>
         <tr r="F4" s="4"/>
         <tr r="M24" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3481003590</v>
+        <v>#N/A Requesting Data...2264739953</v>
         <stp/>
         <stp>BDP|17354182839553220513</stp>
         <tr r="M18" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2961707860</v>
+        <v>#N/A Requesting Data...2354124337</v>
         <stp/>
         <stp>BDP|15833637773500916777</stp>
         <tr r="M22" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3116270412</v>
+        <v>#N/A Requesting Data...2234697273</v>
         <stp/>
         <stp>BDP|10553485173797766561</stp>
         <tr r="M17" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3772991957</v>
+        <v>#N/A Requesting Data...4141333779</v>
         <stp/>
         <stp>BDP|10725320790729783234</stp>
         <tr r="M8" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3498445539</v>
+        <v>#N/A Requesting Data...2594368292</v>
         <stp/>
         <stp>BDP|15290075098549931204</stp>
         <tr r="M2" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3630203178</v>
+        <v>#N/A Requesting Data...1458498545</v>
         <stp/>
         <stp>BDP|11090127615376453378</stp>
         <tr r="M13" s="5"/>
@@ -1159,19 +1188,19 @@
     </main>
     <main first="bofaddin.rtdserver">
       <tp t="s">
-        <v>#N/A Requesting Data...3760933913</v>
+        <v>#N/A Requesting Data...2421228831</v>
         <stp/>
         <stp>BDP|4236539151683226891</stp>
         <tr r="M21" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4277886170</v>
+        <v>#N/A Requesting Data...3245380786</v>
         <stp/>
         <stp>BDP|2613081399981359290</stp>
         <tr r="M12" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2989371238</v>
+        <v>#N/A Requesting Data...4109000424</v>
         <stp/>
         <stp>BDP|2154512199383777756</stp>
         <tr r="M6" s="5"/>
@@ -1189,7 +1218,7 @@
         <tr r="N23" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4075602171</v>
+        <v>#N/A Requesting Data...3960586980</v>
         <stp/>
         <stp>BDP|2219595241806083194</stp>
         <tr r="M15" s="5"/>
@@ -1202,37 +1231,37 @@
         <tr r="E16" s="4"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3421479459</v>
+        <v>#N/A Requesting Data...720591433</v>
         <stp/>
         <stp>BDP|7276645360862777315</stp>
         <tr r="M5" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...2591271917</v>
+        <v>#N/A Requesting Data...2772472289</v>
         <stp/>
         <stp>BDP|1614643148556376256</stp>
         <tr r="M9" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...4290396496</v>
+        <v>#N/A Requesting Data...3269864654</v>
         <stp/>
         <stp>BDP|8389300253224362856</stp>
         <tr r="M4" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3604426337</v>
+        <v>#N/A Requesting Data...3835170269</v>
         <stp/>
         <stp>BDP|1386483162619383929</stp>
         <tr r="M3" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3084482444</v>
+        <v>#N/A Requesting Data...1801494467</v>
         <stp/>
         <stp>BDP|722161999546011081</stp>
         <tr r="M14" s="5"/>
       </tp>
       <tp t="s">
-        <v>#N/A Requesting Data...3281902747</v>
+        <v>#N/A Requesting Data...870105791</v>
         <stp/>
         <stp>BDP|281963796682346956</stp>
         <tr r="M16" s="5"/>
@@ -8222,7 +8251,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3366916-357D-497F-A92B-E1F6043DE334}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -8313,6 +8342,55 @@
       </c>
       <c r="C10" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="90" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -9728,7 +9806,7 @@
       </c>
       <c r="N23">
         <f>IF(M23="USD",1,_xll.BDP(M23&amp;" Curncy", "PX_LAST"))</f>
-        <v>1.3717999999999999</v>
+        <v>1.3902000000000001</v>
       </c>
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>
